--- a/sheets/조재수대금교본/검수/오돌또기.xlsx
+++ b/sheets/조재수대금교본/검수/오돌또기.xlsx
@@ -3452,26 +3452,18 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="S3" s="22"/>
     </row>
     <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B4" s="21"/>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3482,11 +3474,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -3544,11 +3532,7 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -3570,32 +3554,16 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="R6" s="21"/>
       <c r="S6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="23"/>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -3605,19 +3573,11 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L7" s="21"/>
       <c r="M7" s="23"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
       <c r="R7" s="21"/>
       <c r="S7" s="23"/>
@@ -3626,16 +3586,11 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -3649,24 +3604,15 @@
         </is>
       </c>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="M8" s="24"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
@@ -3784,11 +3730,7 @@
     </row>
     <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -3812,11 +3754,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21"/>
       <c r="K11" s="24"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L11" s="21"/>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
@@ -3842,11 +3780,7 @@
     </row>
     <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -3868,11 +3802,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21"/>
       <c r="K12" s="22"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L12" s="21"/>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
@@ -3941,15 +3871,13 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -3970,8 +3898,7 @@
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/오돌또기.xlsx
+++ b/sheets/조재수대금교본/검수/오돌또기.xlsx
@@ -3452,14 +3452,18 @@
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="S3" s="22"/>
     </row>
     <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
@@ -3474,7 +3478,11 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -3532,7 +3540,11 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -3554,16 +3566,32 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
-      <c r="R6" s="21"/>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="S6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
-      <c r="B7" s="21"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
@@ -3573,7 +3601,11 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21"/>
       <c r="K7" s="23"/>
-      <c r="L7" s="21"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23"/>
@@ -3730,7 +3762,11 @@
     </row>
     <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
@@ -3754,7 +3790,11 @@
       <c r="I11" s="24"/>
       <c r="J11" s="21"/>
       <c r="K11" s="24"/>
-      <c r="L11" s="21"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M11" s="24"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
@@ -3780,7 +3820,11 @@
     </row>
     <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
@@ -3802,7 +3846,11 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21"/>
       <c r="K12" s="22"/>
-      <c r="L12" s="21"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/오돌또기.xlsx
+++ b/sheets/조재수대금교본/검수/오돌또기.xlsx
@@ -3352,30 +3352,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3908,7 +3908,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3969,6 +3969,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>